--- a/data/trans_bre/P32-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P32-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,31</t>
+          <t>-3,28; 3,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; -2,05</t>
+          <t>-7,72; -2,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -1,39</t>
+          <t>-7,59; -1,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,18; -3,39</t>
+          <t>-10,35; -2,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 200,08</t>
+          <t>-100,0; 257,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-94,37; -31,87</t>
+          <t>-94,32; -34,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 12,2</t>
+          <t>-100,0; -2,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -38,09</t>
+          <t>-100,0; -31,9</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,35</t>
+          <t>-2,47; 0,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,8; -2,74</t>
+          <t>-6,83; -2,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,43</t>
+          <t>-3,31; 0,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,46; -1,55</t>
+          <t>-6,37; -1,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 18,08</t>
+          <t>-73,79; 23,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,61; -40,14</t>
+          <t>-83,72; -44,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,28; 11,32</t>
+          <t>-56,16; 9,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,43; -32,09</t>
+          <t>-85,23; -26,08</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 0,2</t>
+          <t>-3,74; 0,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 0,46</t>
+          <t>-7,35; 0,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 1,08</t>
+          <t>-5,89; 1,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 0,9</t>
+          <t>-6,17; 0,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-90,88; 35,18</t>
+          <t>-89,33; 24,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,73; 30,53</t>
+          <t>-76,47; 34,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-76,62; 25,67</t>
+          <t>-74,12; 24,46</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,07</t>
+          <t>-2,35; -0,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -3,13</t>
+          <t>-6,12; -3,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -0,53</t>
+          <t>-3,44; -0,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,04; -2,13</t>
+          <t>-5,81; -2,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,02; 2,35</t>
+          <t>-73,81; -4,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-80,29; -49,42</t>
+          <t>-81,47; -51,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-57,07; -11,12</t>
+          <t>-58,7; -11,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,96; -39,36</t>
+          <t>-81,41; -39,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P32-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,52</t>
+          <t>-6,95</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-83,72%</t>
+          <t>-85,44%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 3,6</t>
+          <t>-3,45; 2,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; -2,32</t>
+          <t>-7,54; -1,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,59; -1,3</t>
+          <t>-7,35; -1,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; -2,65</t>
+          <t>-11,17; -3,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 257,15</t>
+          <t>-100,0; 181,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-94,32; -34,78</t>
+          <t>-100,0; -30,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,0</t>
+          <t>-100,0; 31,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -31,9</t>
+          <t>-100,0; -37,59</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,71</t>
+          <t>-2,72</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-64,49%</t>
+          <t>-44,92%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,44</t>
+          <t>-2,49; 0,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,83; -2,85</t>
+          <t>-6,73; -2,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,35</t>
+          <t>-3,15; 0,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -1,33</t>
+          <t>-4,98; -0,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,79; 23,78</t>
+          <t>-75,2; 30,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,72; -44,22</t>
+          <t>-82,62; -42,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 9,93</t>
+          <t>-56,02; 14,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,23; -26,08</t>
+          <t>-69,61; -1,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-2,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-41,95%</t>
+          <t>-35,59%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,35</t>
+          <t>-4,25; 0,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,36</t>
+          <t>-7,33; 0,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1,04</t>
+          <t>-5,66; 1,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 0,71</t>
+          <t>-5,99; 1,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-89,33; 24,15</t>
+          <t>-90,95; 41,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-76,47; 34,78</t>
+          <t>-74,15; 49,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,12; 24,46</t>
+          <t>-71,74; 40,74</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,82</t>
+          <t>-3,07</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-61,43%</t>
+          <t>-47,02%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,35; -0,16</t>
+          <t>-2,36; -0,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,12; -3,2</t>
+          <t>-6,16; -3,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -0,58</t>
+          <t>-3,48; -0,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,81; -2,17</t>
+          <t>-4,88; -0,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,81; -4,48</t>
+          <t>-71,69; 0,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,47; -51,32</t>
+          <t>-81,58; -49,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,7; -11,04</t>
+          <t>-57,5; -8,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,41; -39,04</t>
+          <t>-63,61; -14,33</t>
         </is>
       </c>
     </row>
